--- a/02_Hardware/V1.0/01_筐体/おもり計算 (version 1).xlsx
+++ b/02_Hardware/V1.0/01_筐体/おもり計算 (version 1).xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hirar\Documents\Git\GBA\02_Hardware\V1.0\01_筐体\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F07F26-6EE3-40C1-8188-1E87A982B6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494091D9-65F1-426C-B378-F671E8EB866B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -278,10 +277,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">k </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>k</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -290,6 +285,10 @@
     <rPh sb="11" eb="12">
       <t>マル</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>coff_angle</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2273,9 +2272,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
+    <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.58203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
@@ -2295,7 +2295,7 @@
         <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1" t="s">
         <v>24</v>
@@ -2569,9 +2569,6 @@
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
       <c r="C12">
         <f>ABS(C8*C9/C2)</f>
         <v>5.8428571428571401E-3</v>
@@ -2620,7 +2617,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
       </c>
       <c r="C14">
         <f>(0.5*C19*C18*C11)/(C12*C17)</f>
@@ -2761,6 +2761,12 @@
       <c r="G20">
         <f>DEGREES(ATAN((0.5*G19*(G16^2)*G18*G11)/(G12*G17)))</f>
         <v>68.723627032801403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="C21">
+        <f>DEGREES(ATAN($C$14*C16^2))</f>
+        <v>5.9294612715625368</v>
       </c>
     </row>
   </sheetData>
@@ -2772,18 +2778,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFB8DC1-0901-4004-AEE1-57169980FD59}">
-  <dimension ref="B2:C131"/>
+  <dimension ref="B2:D131"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>4.1739999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:4">
       <c r="B3">
         <v>0</v>
       </c>
@@ -2791,8 +2797,12 @@
         <f>DEGREES(ATAN($C$2*B3^2))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:3">
+      <c r="D3">
+        <f>SQRT(TAN(RADIANS(C3))/$C$2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
       <c r="B4">
         <v>0.1</v>
       </c>
@@ -2800,8 +2810,12 @@
         <f t="shared" ref="C4:C67" si="0">DEGREES(ATAN($C$2*B4^2))</f>
         <v>2.3915256979899938E-2</v>
       </c>
-    </row>
-    <row r="5" spans="2:3">
+      <c r="D4">
+        <f>SQRT(TAN(RADIANS(C4))/$C$2)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5">
         <v>0.2</v>
       </c>
@@ -2809,8 +2823,12 @@
         <f t="shared" si="0"/>
         <v>9.5660944588101454E-2</v>
       </c>
-    </row>
-    <row r="6" spans="2:3">
+      <c r="D5">
+        <f t="shared" ref="D5:D68" si="1">SQRT(TAN(RADIANS(C5))/$C$2)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
       <c r="B6">
         <v>0.3</v>
       </c>
@@ -2818,8 +2836,12 @@
         <f t="shared" si="0"/>
         <v>0.21523631284791431</v>
       </c>
-    </row>
-    <row r="7" spans="2:3">
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
       <c r="B7">
         <v>0.4</v>
       </c>
@@ -2827,8 +2849,12 @@
         <f t="shared" si="0"/>
         <v>0.38263844527867291</v>
       </c>
-    </row>
-    <row r="8" spans="2:3">
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
       <c r="B8">
         <v>0.5</v>
       </c>
@@ -2836,8 +2862,12 @@
         <f t="shared" si="0"/>
         <v>0.59785975968712479</v>
       </c>
-    </row>
-    <row r="9" spans="2:3">
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
       <c r="B9">
         <v>0.6</v>
       </c>
@@ -2845,8 +2875,12 @@
         <f t="shared" si="0"/>
         <v>0.86088451136437993</v>
       </c>
-    </row>
-    <row r="10" spans="2:3">
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
       <c r="B10">
         <v>0.7</v>
       </c>
@@ -2854,8 +2888,12 @@
         <f t="shared" si="0"/>
         <v>1.1716843029864481</v>
       </c>
-    </row>
-    <row r="11" spans="2:3">
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
       <c r="B11">
         <v>0.8</v>
       </c>
@@ -2863,8 +2901,12 @@
         <f t="shared" si="0"/>
         <v>1.530212609891503</v>
       </c>
-    </row>
-    <row r="12" spans="2:3">
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
       <c r="B12">
         <v>0.9</v>
       </c>
@@ -2872,8 +2914,12 @@
         <f t="shared" si="0"/>
         <v>1.9363983361193211</v>
       </c>
-    </row>
-    <row r="13" spans="2:3">
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
       <c r="B13">
         <v>1</v>
       </c>
@@ -2881,8 +2927,12 @@
         <f t="shared" si="0"/>
         <v>2.3901384261256804</v>
       </c>
-    </row>
-    <row r="14" spans="2:3">
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
       <c r="B14">
         <v>1.1000000000000001</v>
       </c>
@@ -2890,8 +2940,12 @@
         <f t="shared" si="0"/>
         <v>2.8912895698578218</v>
       </c>
-    </row>
-    <row r="15" spans="2:3">
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
       <c r="B15">
         <v>1.2</v>
       </c>
@@ -2899,8 +2953,12 @@
         <f t="shared" si="0"/>
         <v>3.4396590552528883</v>
       </c>
-    </row>
-    <row r="16" spans="2:3">
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
       <c r="B16">
         <v>1.3</v>
       </c>
@@ -2908,8 +2966,12 @@
         <f t="shared" si="0"/>
         <v>4.0349948424454514</v>
       </c>
-    </row>
-    <row r="17" spans="2:3">
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
       <c r="B17">
         <v>1.4</v>
       </c>
@@ -2917,8 +2979,12 @@
         <f t="shared" si="0"/>
         <v>4.6769749581337861</v>
       </c>
-    </row>
-    <row r="18" spans="2:3">
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
       <c r="B18">
         <v>1.5</v>
       </c>
@@ -2926,8 +2992,12 @@
         <f t="shared" si="0"/>
         <v>5.3651963365424242</v>
       </c>
-    </row>
-    <row r="19" spans="2:3">
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>1.5000000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
       <c r="B19">
         <v>1.6</v>
       </c>
@@ -2935,8 +3005,12 @@
         <f t="shared" si="0"/>
         <v>6.099163264852951</v>
       </c>
-    </row>
-    <row r="20" spans="2:3">
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
       <c r="B20">
         <v>1.7</v>
       </c>
@@ -2944,8 +3018,12 @@
         <f t="shared" si="0"/>
         <v>6.87827562516018</v>
       </c>
-    </row>
-    <row r="21" spans="2:3">
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
       <c r="B21">
         <v>1.8</v>
       </c>
@@ -2953,8 +3031,12 @@
         <f t="shared" si="0"/>
         <v>7.7018171608809487</v>
       </c>
-    </row>
-    <row r="22" spans="2:3">
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
       <c r="B22">
         <v>1.9</v>
       </c>
@@ -2962,8 +3044,12 @@
         <f t="shared" si="0"/>
         <v>8.5689440316258949</v>
       </c>
-    </row>
-    <row r="23" spans="2:3">
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
       <c r="B23">
         <v>2</v>
       </c>
@@ -2971,8 +3057,12 @@
         <f t="shared" si="0"/>
         <v>9.4786739549487784</v>
       </c>
-    </row>
-    <row r="24" spans="2:3">
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
       <c r="B24">
         <v>2.1</v>
       </c>
@@ -2980,8 +3070,12 @@
         <f t="shared" si="0"/>
         <v>10.429876263821164</v>
       </c>
-    </row>
-    <row r="25" spans="2:3">
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
       <c r="B25">
         <v>2.2000000000000002</v>
       </c>
@@ -2989,8 +3083,12 @@
         <f t="shared" si="0"/>
         <v>11.421263232517134</v>
       </c>
-    </row>
-    <row r="26" spans="2:3">
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
       <c r="B26">
         <v>2.2999999999999998</v>
       </c>
@@ -2998,8 +3096,12 @@
         <f t="shared" si="0"/>
         <v>12.451383037990714</v>
       </c>
-    </row>
-    <row r="27" spans="2:3">
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
       <c r="B27">
         <v>2.4</v>
       </c>
@@ -3007,8 +3109,12 @@
         <f t="shared" si="0"/>
         <v>13.518614725907701</v>
       </c>
-    </row>
-    <row r="28" spans="2:3">
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
       <c r="B28">
         <v>2.5</v>
       </c>
@@ -3016,8 +3122,12 @@
         <f t="shared" si="0"/>
         <v>14.621165537565172</v>
       </c>
-    </row>
-    <row r="29" spans="2:3">
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
       <c r="B29">
         <v>2.6</v>
       </c>
@@ -3025,8 +3135,12 @@
         <f t="shared" si="0"/>
         <v>15.75707092378164</v>
       </c>
-    </row>
-    <row r="30" spans="2:3">
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
       <c r="B30">
         <v>2.7</v>
       </c>
@@ -3034,8 +3148,12 @@
         <f t="shared" si="0"/>
         <v>16.92419752302742</v>
       </c>
-    </row>
-    <row r="31" spans="2:3">
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
       <c r="B31">
         <v>2.8</v>
       </c>
@@ -3043,8 +3161,12 @@
         <f t="shared" si="0"/>
         <v>18.120249313222317</v>
       </c>
-    </row>
-    <row r="32" spans="2:3">
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
       <c r="B32">
         <v>2.9</v>
       </c>
@@ -3052,8 +3174,12 @@
         <f t="shared" si="0"/>
         <v>19.342777060715605</v>
       </c>
-    </row>
-    <row r="33" spans="2:3">
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
       <c r="B33">
         <v>3</v>
       </c>
@@ -3061,8 +3187,12 @@
         <f t="shared" si="0"/>
         <v>20.58919108843395</v>
       </c>
-    </row>
-    <row r="34" spans="2:3">
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
       <c r="B34">
         <v>3.1</v>
       </c>
@@ -3070,8 +3200,12 @@
         <f t="shared" si="0"/>
         <v>21.856777272017318</v>
       </c>
-    </row>
-    <row r="35" spans="2:3">
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
       <c r="B35">
         <v>3.2</v>
       </c>
@@ -3079,8 +3213,12 @@
         <f t="shared" si="0"/>
         <v>23.142716053347495</v>
       </c>
-    </row>
-    <row r="36" spans="2:3">
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
       <c r="B36">
         <v>3.3</v>
       </c>
@@ -3088,8 +3226,12 @@
         <f t="shared" si="0"/>
         <v>24.444104141703132</v>
       </c>
-    </row>
-    <row r="37" spans="2:3">
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
       <c r="B37">
         <v>3.4</v>
       </c>
@@ -3097,8 +3239,12 @@
         <f t="shared" si="0"/>
         <v>25.757978460990234</v>
       </c>
-    </row>
-    <row r="38" spans="2:3">
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
       <c r="B38">
         <v>3.5</v>
       </c>
@@ -3106,8 +3252,12 @@
         <f t="shared" si="0"/>
         <v>27.081341804295974</v>
       </c>
-    </row>
-    <row r="39" spans="2:3">
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
       <c r="B39">
         <v>3.6</v>
       </c>
@@ -3115,8 +3265,12 @@
         <f t="shared" si="0"/>
         <v>28.411189580998855</v>
       </c>
-    </row>
-    <row r="40" spans="2:3">
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
       <c r="B40">
         <v>3.7</v>
       </c>
@@ -3124,8 +3278,12 @@
         <f t="shared" si="0"/>
         <v>29.744536992198743</v>
       </c>
-    </row>
-    <row r="41" spans="2:3">
+      <c r="D40">
+        <f t="shared" si="1"/>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
       <c r="B41">
         <v>3.8</v>
       </c>
@@ -3133,8 +3291,12 @@
         <f t="shared" si="0"/>
         <v>31.078445950879825</v>
       </c>
-    </row>
-    <row r="42" spans="2:3">
+      <c r="D41">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
       <c r="B42">
         <v>3.9</v>
       </c>
@@ -3142,8 +3304,12 @@
         <f t="shared" si="0"/>
         <v>32.410051075395444</v>
       </c>
-    </row>
-    <row r="43" spans="2:3">
+      <c r="D42">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
       <c r="B43">
         <v>4</v>
       </c>
@@ -3151,8 +3317,12 @@
         <f t="shared" si="0"/>
         <v>33.736584127660429</v>
       </c>
-    </row>
-    <row r="44" spans="2:3">
+      <c r="D43">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
       <c r="B44">
         <v>4.0999999999999996</v>
       </c>
@@ -3160,8 +3330,12 @@
         <f t="shared" si="0"/>
         <v>35.055396337729242</v>
       </c>
-    </row>
-    <row r="45" spans="2:3">
+      <c r="D44">
+        <f t="shared" si="1"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
       <c r="B45">
         <v>4.2</v>
       </c>
@@ -3169,8 +3343,12 @@
         <f t="shared" si="0"/>
         <v>36.363978149214013</v>
       </c>
-    </row>
-    <row r="46" spans="2:3">
+      <c r="D45">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
       <c r="B46">
         <v>4.3</v>
       </c>
@@ -3178,8 +3356,12 @@
         <f t="shared" si="0"/>
         <v>37.659976028869885</v>
       </c>
-    </row>
-    <row r="47" spans="2:3">
+      <c r="D46">
+        <f t="shared" si="1"/>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
       <c r="B47">
         <v>4.4000000000000004</v>
       </c>
@@ -3187,8 +3369,12 @@
         <f t="shared" si="0"/>
         <v>38.94120610151554</v>
       </c>
-    </row>
-    <row r="48" spans="2:3">
+      <c r="D47">
+        <f t="shared" si="1"/>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
       <c r="B48">
         <v>4.5</v>
       </c>
@@ -3196,8 +3382,12 @@
         <f t="shared" si="0"/>
         <v>40.2056644910503</v>
       </c>
-    </row>
-    <row r="49" spans="2:3">
+      <c r="D48">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
       <c r="B49">
         <v>4.5999999999999996</v>
       </c>
@@ -3205,8 +3395,12 @@
         <f t="shared" si="0"/>
         <v>41.451534362987609</v>
       </c>
-    </row>
-    <row r="50" spans="2:3">
+      <c r="D49">
+        <f t="shared" si="1"/>
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
       <c r="B50">
         <v>4.7</v>
       </c>
@@ -3214,8 +3408,12 @@
         <f t="shared" si="0"/>
         <v>42.677189767975364</v>
       </c>
-    </row>
-    <row r="51" spans="2:3">
+      <c r="D50">
+        <f t="shared" si="1"/>
+        <v>4.7000000000000011</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
       <c r="B51">
         <v>4.8</v>
       </c>
@@ -3223,8 +3421,12 @@
         <f t="shared" si="0"/>
         <v>43.881196474903959</v>
       </c>
-    </row>
-    <row r="52" spans="2:3">
+      <c r="D51">
+        <f t="shared" si="1"/>
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
       <c r="B52">
         <v>4.9000000000000004</v>
       </c>
@@ -3232,8 +3434,12 @@
         <f t="shared" si="0"/>
         <v>45.062310053609281</v>
       </c>
-    </row>
-    <row r="53" spans="2:3">
+      <c r="D52">
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
       <c r="B53">
         <v>5</v>
       </c>
@@ -3241,8 +3447,12 @@
         <f t="shared" si="0"/>
         <v>46.219471519573801</v>
       </c>
-    </row>
-    <row r="54" spans="2:3">
+      <c r="D53">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
       <c r="B54">
         <v>5.0999999999999996</v>
       </c>
@@ -3250,8 +3460,12 @@
         <f t="shared" si="0"/>
         <v>47.351800886498978</v>
       </c>
-    </row>
-    <row r="55" spans="2:3">
+      <c r="D54">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
       <c r="B55">
         <v>5.2</v>
       </c>
@@ -3259,8 +3473,12 @@
         <f t="shared" si="0"/>
         <v>48.458588988382367</v>
       </c>
-    </row>
-    <row r="56" spans="2:3">
+      <c r="D55">
+        <f t="shared" si="1"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
       <c r="B56">
         <v>5.3</v>
       </c>
@@ -3268,8 +3486,12 @@
         <f t="shared" si="0"/>
         <v>49.539287932846065</v>
       </c>
-    </row>
-    <row r="57" spans="2:3">
+      <c r="D56">
+        <f t="shared" si="1"/>
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
       <c r="B57">
         <v>5.4</v>
       </c>
@@ -3277,8 +3499,12 @@
         <f t="shared" si="0"/>
         <v>50.593500534526875</v>
       </c>
-    </row>
-    <row r="58" spans="2:3">
+      <c r="D57">
+        <f t="shared" si="1"/>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
       <c r="B58">
         <v>5.5</v>
       </c>
@@ -3286,8 +3512,12 @@
         <f t="shared" si="0"/>
         <v>51.620969054202554</v>
       </c>
-    </row>
-    <row r="59" spans="2:3">
+      <c r="D58">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
       <c r="B59">
         <v>5.6</v>
       </c>
@@ -3295,8 +3525,12 @@
         <f t="shared" si="0"/>
         <v>52.621563538852129</v>
       </c>
-    </row>
-    <row r="60" spans="2:3">
+      <c r="D59">
+        <f t="shared" si="1"/>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
       <c r="B60">
         <v>5.7</v>
       </c>
@@ -3304,8 +3538,12 @@
         <f t="shared" si="0"/>
         <v>53.595270022706231</v>
       </c>
-    </row>
-    <row r="61" spans="2:3">
+      <c r="D60">
+        <f t="shared" si="1"/>
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
       <c r="B61">
         <v>5.8</v>
       </c>
@@ -3313,8 +3551,12 @@
         <f t="shared" si="0"/>
         <v>54.542178811902794</v>
       </c>
-    </row>
-    <row r="62" spans="2:3">
+      <c r="D61">
+        <f t="shared" si="1"/>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
       <c r="B62">
         <v>5.9</v>
       </c>
@@ -3322,8 +3564,12 @@
         <f t="shared" si="0"/>
         <v>55.462473037600056</v>
       </c>
-    </row>
-    <row r="63" spans="2:3">
+      <c r="D62">
+        <f t="shared" si="1"/>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
       <c r="B63">
         <v>6</v>
       </c>
@@ -3331,8 +3577,12 @@
         <f t="shared" si="0"/>
         <v>56.356417625873945</v>
       </c>
-    </row>
-    <row r="64" spans="2:3">
+      <c r="D63">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
       <c r="B64">
         <v>6.1</v>
       </c>
@@ -3340,8 +3590,12 @@
         <f t="shared" si="0"/>
         <v>57.22434879859312</v>
       </c>
-    </row>
-    <row r="65" spans="2:3">
+      <c r="D64">
+        <f t="shared" si="1"/>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
       <c r="B65">
         <v>6.2</v>
       </c>
@@ -3349,8 +3603,12 @@
         <f t="shared" si="0"/>
         <v>58.066664188500717</v>
       </c>
-    </row>
-    <row r="66" spans="2:3">
+      <c r="D65">
+        <f t="shared" si="1"/>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
       <c r="B66">
         <v>6.3</v>
       </c>
@@ -3358,8 +3616,12 @@
         <f t="shared" si="0"/>
         <v>58.883813624389539</v>
       </c>
-    </row>
-    <row r="67" spans="2:3">
+      <c r="D66">
+        <f t="shared" si="1"/>
+        <v>6.3000000000000007</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
       <c r="B67">
         <v>6.4</v>
       </c>
@@ -3367,581 +3629,841 @@
         <f t="shared" si="0"/>
         <v>59.67629061872519</v>
       </c>
-    </row>
-    <row r="68" spans="2:3">
+      <c r="D67">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
       <c r="B68">
         <v>6.5</v>
       </c>
       <c r="C68">
-        <f t="shared" ref="C68:C131" si="1">DEGREES(ATAN($C$2*B68^2))</f>
+        <f t="shared" ref="C68:C131" si="2">DEGREES(ATAN($C$2*B68^2))</f>
         <v>60.444624570326937</v>
       </c>
-    </row>
-    <row r="69" spans="2:3">
+      <c r="D68">
+        <f t="shared" si="1"/>
+        <v>6.4999999999999991</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
       <c r="B69">
         <v>6.6</v>
       </c>
       <c r="C69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>61.189373678584154</v>
       </c>
-    </row>
-    <row r="70" spans="2:3">
+      <c r="D69">
+        <f t="shared" ref="D69:D131" si="3">SQRT(TAN(RADIANS(C69))/$C$2)</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
       <c r="B70">
         <v>6.7</v>
       </c>
       <c r="C70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>61.911118552888134</v>
       </c>
-    </row>
-    <row r="71" spans="2:3">
+      <c r="D70">
+        <f t="shared" si="3"/>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
       <c r="B71">
         <v>6.8</v>
       </c>
       <c r="C71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>62.610456491152206</v>
       </c>
-    </row>
-    <row r="72" spans="2:3">
+      <c r="D71">
+        <f t="shared" si="3"/>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
       <c r="B72">
         <v>6.9</v>
       </c>
       <c r="C72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63.287996394104319</v>
       </c>
-    </row>
-    <row r="73" spans="2:3">
+      <c r="D72">
+        <f t="shared" si="3"/>
+        <v>6.9000000000000012</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
       <c r="B73">
         <v>7</v>
       </c>
       <c r="C73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63.944354277087427</v>
       </c>
-    </row>
-    <row r="74" spans="2:3">
+      <c r="D73">
+        <f t="shared" si="3"/>
+        <v>6.9999999999999991</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
       <c r="B74">
         <v>7.1</v>
       </c>
       <c r="C74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>64.580149338028974</v>
       </c>
-    </row>
-    <row r="75" spans="2:3">
+      <c r="D74">
+        <f t="shared" si="3"/>
+        <v>7.1000000000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
       <c r="B75">
         <v>7.2</v>
       </c>
       <c r="C75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>65.196000538700446</v>
       </c>
-    </row>
-    <row r="76" spans="2:3">
+      <c r="D75">
+        <f t="shared" si="3"/>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
       <c r="B76">
         <v>7.3</v>
       </c>
       <c r="C76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>65.79252365607492</v>
       </c>
-    </row>
-    <row r="77" spans="2:3">
+      <c r="D76">
+        <f t="shared" si="3"/>
+        <v>7.3000000000000007</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
       <c r="B77">
         <v>7.4</v>
       </c>
       <c r="C77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66.370328761231434</v>
       </c>
-    </row>
-    <row r="78" spans="2:3">
+      <c r="D77">
+        <f t="shared" si="3"/>
+        <v>7.4000000000000012</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
       <c r="B78">
         <v>7.5</v>
       </c>
       <c r="C78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66.930018084617174</v>
       </c>
-    </row>
-    <row r="79" spans="2:3">
+      <c r="D78">
+        <f t="shared" si="3"/>
+        <v>7.5000000000000018</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
       <c r="B79">
         <v>7.6</v>
       </c>
       <c r="C79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>67.472184228361968</v>
       </c>
-    </row>
-    <row r="80" spans="2:3">
+      <c r="D79">
+        <f t="shared" si="3"/>
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
       <c r="B80">
         <v>7.7</v>
       </c>
       <c r="C80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>67.997408688580904</v>
       </c>
-    </row>
-    <row r="81" spans="2:3">
+      <c r="D80">
+        <f t="shared" si="3"/>
+        <v>7.6999999999999993</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
       <c r="B81">
         <v>7.8</v>
       </c>
       <c r="C81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>68.506260653064402</v>
       </c>
-    </row>
-    <row r="82" spans="2:3">
+      <c r="D81">
+        <f t="shared" si="3"/>
+        <v>7.8000000000000034</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
       <c r="B82">
         <v>7.9</v>
       </c>
       <c r="C82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>68.999296042334976</v>
       </c>
-    </row>
-    <row r="83" spans="2:3">
+      <c r="D82">
+        <f t="shared" si="3"/>
+        <v>7.8999999999999995</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
       <c r="B83">
         <v>8</v>
       </c>
       <c r="C83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69.477056764661157</v>
       </c>
-    </row>
-    <row r="84" spans="2:3">
+      <c r="D83">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
       <c r="B84">
         <v>8.1</v>
       </c>
       <c r="C84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69.940070158197713</v>
       </c>
-    </row>
-    <row r="85" spans="2:3">
+      <c r="D84">
+        <f t="shared" si="3"/>
+        <v>8.1000000000000014</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
       <c r="B85">
         <v>8.1999999999999993</v>
       </c>
       <c r="C85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>70.38884859592136</v>
       </c>
-    </row>
-    <row r="86" spans="2:3">
+      <c r="D85">
+        <f t="shared" si="3"/>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
       <c r="B86">
         <v>8.3000000000000096</v>
       </c>
       <c r="C86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>70.823889231416942</v>
       </c>
-    </row>
-    <row r="87" spans="2:3">
+      <c r="D86">
+        <f t="shared" si="3"/>
+        <v>8.3000000000000131</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
       <c r="B87">
         <v>8.4</v>
       </c>
       <c r="C87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>71.245673865818787</v>
       </c>
-    </row>
-    <row r="88" spans="2:3">
+      <c r="D87">
+        <f t="shared" si="3"/>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
       <c r="B88">
         <v>8.5</v>
       </c>
       <c r="C88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>71.654668918314272</v>
       </c>
-    </row>
-    <row r="89" spans="2:3">
+      <c r="D88">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
       <c r="B89">
         <v>8.6000000000000103</v>
       </c>
       <c r="C89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72.051325484557623</v>
       </c>
-    </row>
-    <row r="90" spans="2:3">
+      <c r="D89">
+        <f t="shared" si="3"/>
+        <v>8.6000000000000085</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
       <c r="B90">
         <v>8.7000000000000099</v>
       </c>
       <c r="C90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72.436079469130803</v>
       </c>
-    </row>
-    <row r="91" spans="2:3">
+      <c r="D90">
+        <f t="shared" si="3"/>
+        <v>8.7000000000000117</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
       <c r="B91">
         <v>8.8000000000000096</v>
       </c>
       <c r="C91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72.809351779816552</v>
       </c>
-    </row>
-    <row r="92" spans="2:3">
+      <c r="D91">
+        <f t="shared" si="3"/>
+        <v>8.8000000000000096</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
       <c r="B92">
         <v>8.9</v>
       </c>
       <c r="C92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>73.17154857292806</v>
       </c>
-    </row>
-    <row r="93" spans="2:3">
+      <c r="D92">
+        <f t="shared" si="3"/>
+        <v>8.8999999999999986</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
       <c r="B93">
         <v>9.0000000000000107</v>
       </c>
       <c r="C93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>73.523061540276032</v>
       </c>
-    </row>
-    <row r="94" spans="2:3">
+      <c r="D93">
+        <f t="shared" si="3"/>
+        <v>9.0000000000000142</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
       <c r="B94">
         <v>9.1000000000000192</v>
       </c>
       <c r="C94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>73.864268229554</v>
       </c>
-    </row>
-    <row r="95" spans="2:3">
+      <c r="D94">
+        <f t="shared" si="3"/>
+        <v>9.1000000000000174</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
       <c r="B95">
         <v>9.2000000000000295</v>
       </c>
       <c r="C95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>74.195532390999304</v>
       </c>
-    </row>
-    <row r="96" spans="2:3">
+      <c r="D95">
+        <f t="shared" si="3"/>
+        <v>9.2000000000000295</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
       <c r="B96">
         <v>9.3000000000000398</v>
       </c>
       <c r="C96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>74.51720434414365</v>
       </c>
-    </row>
-    <row r="97" spans="2:3">
+      <c r="D96">
+        <f t="shared" si="3"/>
+        <v>9.300000000000038</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
       <c r="B97">
         <v>9.4000000000000501</v>
       </c>
       <c r="C97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>74.829621359321834</v>
       </c>
-    </row>
-    <row r="98" spans="2:3">
+      <c r="D97">
+        <f t="shared" si="3"/>
+        <v>9.4000000000000483</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
       <c r="B98">
         <v>9.5000000000000604</v>
       </c>
       <c r="C98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75.133108049360686</v>
       </c>
-    </row>
-    <row r="99" spans="2:3">
+      <c r="D98">
+        <f t="shared" si="3"/>
+        <v>9.5000000000000622</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
       <c r="B99">
         <v>9.6000000000000707</v>
       </c>
       <c r="C99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75.427976767538055</v>
       </c>
-    </row>
-    <row r="100" spans="2:3">
+      <c r="D99">
+        <f t="shared" si="3"/>
+        <v>9.6000000000000707</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
       <c r="B100">
         <v>9.7000000000000792</v>
       </c>
       <c r="C100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75.714528008488912</v>
       </c>
-    </row>
-    <row r="101" spans="2:3">
+      <c r="D100">
+        <f t="shared" si="3"/>
+        <v>9.7000000000000774</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
       <c r="B101">
         <v>9.8000000000000895</v>
       </c>
       <c r="C101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75.993050809251301</v>
       </c>
-    </row>
-    <row r="102" spans="2:3">
+      <c r="D101">
+        <f t="shared" si="3"/>
+        <v>9.8000000000000895</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
       <c r="B102">
         <v>9.9000000000000998</v>
       </c>
       <c r="C102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76.263823148096989</v>
       </c>
-    </row>
-    <row r="103" spans="2:3">
+      <c r="D102">
+        <f t="shared" si="3"/>
+        <v>9.9000000000000963</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
       <c r="B103">
         <v>10.000000000000099</v>
       </c>
       <c r="C103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76.52711233918609</v>
       </c>
-    </row>
-    <row r="104" spans="2:3">
+      <c r="D103">
+        <f t="shared" si="3"/>
+        <v>10.000000000000107</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
       <c r="B104">
         <v>10.100000000000099</v>
       </c>
       <c r="C104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76.783175421428723</v>
       </c>
-    </row>
-    <row r="105" spans="2:3">
+      <c r="D104">
+        <f t="shared" si="3"/>
+        <v>10.100000000000099</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
       <c r="B105">
         <v>10.200000000000101</v>
       </c>
       <c r="C105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77.032259540235316</v>
       </c>
-    </row>
-    <row r="106" spans="2:3">
+      <c r="D105">
+        <f t="shared" si="3"/>
+        <v>10.200000000000108</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
       <c r="B106">
         <v>10.3000000000001</v>
       </c>
       <c r="C106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77.274602321095344</v>
       </c>
-    </row>
-    <row r="107" spans="2:3">
+      <c r="D106">
+        <f t="shared" si="3"/>
+        <v>10.300000000000098</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
       <c r="B107">
         <v>10.400000000000199</v>
       </c>
       <c r="C107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77.510432234148894</v>
       </c>
-    </row>
-    <row r="108" spans="2:3">
+      <c r="D107">
+        <f t="shared" si="3"/>
+        <v>10.400000000000199</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
       <c r="B108">
         <v>10.500000000000201</v>
       </c>
       <c r="C108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77.739968949103996</v>
       </c>
-    </row>
-    <row r="109" spans="2:3">
+      <c r="D108">
+        <f t="shared" si="3"/>
+        <v>10.500000000000208</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
       <c r="B109">
         <v>10.6000000000002</v>
       </c>
       <c r="C109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77.963423680024505</v>
       </c>
-    </row>
-    <row r="110" spans="2:3">
+      <c r="D109">
+        <f t="shared" si="3"/>
+        <v>10.600000000000202</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
       <c r="B110">
         <v>10.7000000000002</v>
       </c>
       <c r="C110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78.180999519644161</v>
       </c>
-    </row>
-    <row r="111" spans="2:3">
+      <c r="D110">
+        <f t="shared" si="3"/>
+        <v>10.700000000000198</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
       <c r="B111">
         <v>10.8000000000002</v>
       </c>
       <c r="C111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78.392891762991297</v>
       </c>
-    </row>
-    <row r="112" spans="2:3">
+      <c r="D111">
+        <f t="shared" si="3"/>
+        <v>10.800000000000198</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
       <c r="B112">
         <v>10.900000000000199</v>
       </c>
       <c r="C112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78.599288220204812</v>
       </c>
-    </row>
-    <row r="113" spans="2:3">
+      <c r="D112">
+        <f t="shared" si="3"/>
+        <v>10.900000000000205</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
       <c r="B113">
         <v>11.000000000000201</v>
       </c>
       <c r="C113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78.800369518509257</v>
       </c>
-    </row>
-    <row r="114" spans="2:3">
+      <c r="D113">
+        <f t="shared" si="3"/>
+        <v>11.000000000000199</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
       <c r="B114">
         <v>11.1000000000002</v>
       </c>
       <c r="C114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78.996309393387875</v>
       </c>
-    </row>
-    <row r="115" spans="2:3">
+      <c r="D114">
+        <f t="shared" si="3"/>
+        <v>11.100000000000202</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
       <c r="B115">
         <v>11.2000000000002</v>
       </c>
       <c r="C115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.187274969051728</v>
       </c>
-    </row>
-    <row r="116" spans="2:3">
+      <c r="D115">
+        <f t="shared" si="3"/>
+        <v>11.200000000000202</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
       <c r="B116">
         <v>11.3000000000002</v>
       </c>
       <c r="C116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.373427028352296</v>
       </c>
-    </row>
-    <row r="117" spans="2:3">
+      <c r="D116">
+        <f t="shared" si="3"/>
+        <v>11.300000000000201</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
       <c r="B117">
         <v>11.400000000000301</v>
       </c>
       <c r="C117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.554920272324509</v>
       </c>
-    </row>
-    <row r="118" spans="2:3">
+      <c r="D117">
+        <f t="shared" si="3"/>
+        <v>11.400000000000299</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
       <c r="B118">
         <v>11.5000000000003</v>
       </c>
       <c r="C118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.731903569578165</v>
       </c>
-    </row>
-    <row r="119" spans="2:3">
+      <c r="D118">
+        <f t="shared" si="3"/>
+        <v>11.500000000000302</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
       <c r="B119">
         <v>11.6000000000003</v>
       </c>
       <c r="C119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.904520195784443</v>
       </c>
-    </row>
-    <row r="120" spans="2:3">
+      <c r="D119">
+        <f t="shared" si="3"/>
+        <v>11.600000000000298</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
       <c r="B120">
         <v>11.700000000000299</v>
       </c>
       <c r="C120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.072908063517986</v>
       </c>
-    </row>
-    <row r="121" spans="2:3">
+      <c r="D120">
+        <f t="shared" si="3"/>
+        <v>11.700000000000298</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
       <c r="B121">
         <v>11.800000000000299</v>
       </c>
       <c r="C121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.237199942735216</v>
       </c>
-    </row>
-    <row r="122" spans="2:3">
+      <c r="D121">
+        <f t="shared" si="3"/>
+        <v>11.800000000000303</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
       <c r="B122">
         <v>11.900000000000301</v>
       </c>
       <c r="C122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.397523672176675</v>
       </c>
-    </row>
-    <row r="123" spans="2:3">
+      <c r="D122">
+        <f t="shared" si="3"/>
+        <v>11.900000000000299</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
       <c r="B123">
         <v>12.0000000000003</v>
       </c>
       <c r="C123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.554002361989163</v>
       </c>
-    </row>
-    <row r="124" spans="2:3">
+      <c r="D123">
+        <f t="shared" si="3"/>
+        <v>12.000000000000298</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
       <c r="B124">
         <v>12.1000000000003</v>
       </c>
       <c r="C124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.70675458786684</v>
       </c>
-    </row>
-    <row r="125" spans="2:3">
+      <c r="D124">
+        <f t="shared" si="3"/>
+        <v>12.100000000000296</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
       <c r="B125">
         <v>12.200000000000299</v>
       </c>
       <c r="C125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80.855894577012037</v>
       </c>
-    </row>
-    <row r="126" spans="2:3">
+      <c r="D125">
+        <f t="shared" si="3"/>
+        <v>12.200000000000301</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
       <c r="B126">
         <v>12.3000000000004</v>
       </c>
       <c r="C126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.001532386215843</v>
       </c>
-    </row>
-    <row r="127" spans="2:3">
+      <c r="D126">
+        <f t="shared" si="3"/>
+        <v>12.300000000000402</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
       <c r="B127">
         <v>12.4000000000004</v>
       </c>
       <c r="C127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.143774072354674</v>
       </c>
-    </row>
-    <row r="128" spans="2:3">
+      <c r="D127">
+        <f t="shared" si="3"/>
+        <v>12.400000000000396</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
       <c r="B128">
         <v>12.5000000000004</v>
       </c>
       <c r="C128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.282721855598481</v>
       </c>
-    </row>
-    <row r="129" spans="2:3">
+      <c r="D128">
+        <f t="shared" si="3"/>
+        <v>12.500000000000396</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
       <c r="B129">
         <v>12.600000000000399</v>
       </c>
       <c r="C129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.41847427561558</v>
       </c>
-    </row>
-    <row r="130" spans="2:3">
+      <c r="D129">
+        <f t="shared" si="3"/>
+        <v>12.600000000000396</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
       <c r="B130">
         <v>12.700000000000401</v>
       </c>
       <c r="C130">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.551126341058307</v>
       </c>
-    </row>
-    <row r="131" spans="2:3">
+      <c r="D130">
+        <f t="shared" si="3"/>
+        <v>12.700000000000404</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131">
         <v>12.8000000000004</v>
       </c>
       <c r="C131">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81.680769672603915</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="3"/>
+        <v>12.800000000000402</v>
       </c>
     </row>
   </sheetData>

--- a/02_Hardware/V1.0/01_筐体/おもり計算 (version 1).xlsx
+++ b/02_Hardware/V1.0/01_筐体/おもり計算 (version 1).xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hirar\Documents\Git\GBA\02_Hardware\V1.0\01_筐体\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494091D9-65F1-426C-B378-F671E8EB866B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3148615-5AD3-4985-A5BD-79CF7C6EA5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="計算シート" sheetId="3" r:id="rId1"/>
+    <sheet name="グラフ1" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
   <si>
     <t>V0.0</t>
     <phoneticPr fontId="1"/>
@@ -289,6 +291,242 @@
   </si>
   <si>
     <t>coff_angle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>密度</t>
+    <rPh sb="0" eb="2">
+      <t>ミツド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kg/m^3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支柱から球中心までの距離</t>
+    <rPh sb="5" eb="7">
+      <t>チュウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>球</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質量</t>
+    <rPh sb="0" eb="2">
+      <t>シツリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長さ</t>
+    <rPh sb="0" eb="1">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支柱から錘中心までの距離</t>
+    <rPh sb="5" eb="7">
+      <t>チュウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>錘</t>
+    <rPh sb="0" eb="1">
+      <t>オモリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外径</t>
+    <rPh sb="0" eb="2">
+      <t>ガイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内径</t>
+    <rPh sb="0" eb="2">
+      <t>ナイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内径</t>
+    <rPh sb="0" eb="2">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>密度</t>
+    <rPh sb="0" eb="2">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モーメント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロッド重心位置</t>
+  </si>
+  <si>
+    <t>ロッド重心位置</t>
+    <rPh sb="3" eb="5">
+      <t>ジュウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重心位置</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>等価質量</t>
+    <rPh sb="0" eb="2">
+      <t>トウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シツリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>投影面積</t>
+    <rPh sb="0" eb="4">
+      <t>トウエイメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m^2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>係数</t>
+    <rPh sb="0" eb="2">
+      <t>ケイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>錘オフセット量</t>
+    <rPh sb="0" eb="1">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m/s^2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力加速度</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大気密度</t>
+    <rPh sb="0" eb="2">
+      <t>タイキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ミツド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>角度</t>
+    <rPh sb="0" eb="2">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大角度</t>
+    <rPh sb="0" eb="4">
+      <t>サイダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>deg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風速</t>
+    <rPh sb="0" eb="2">
+      <t>フウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大風速</t>
+    <rPh sb="0" eb="2">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1m/sでの角度</t>
+    <rPh sb="6" eb="8">
+      <t>カクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3m/sでの角度</t>
+    <rPh sb="6" eb="8">
+      <t>カクド</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -338,9 +576,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -372,37 +611,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -829,388 +1038,388 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3915256979899938E-2</c:v>
+                  <c:v>2.8441999480523394E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.5660944588101454E-2</c:v>
+                  <c:v>0.1137678577491741</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21523631284791431</c:v>
+                  <c:v>0.25597631326584203</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.38263844527867291</c:v>
+                  <c:v>0.45506246026806418</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.59785975968712479</c:v>
+                  <c:v>0.71101354533522709</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.86088451136437993</c:v>
+                  <c:v>1.0238030875477691</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1716843029864481</c:v>
+                  <c:v>1.3933833324626947</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.530212609891503</c:v>
+                  <c:v>1.8196760605208775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.9363983361193211</c:v>
+                  <c:v>2.3025617864233912</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3901384261256804</c:v>
+                  <c:v>2.8418674085524871</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.8912895698578218</c:v>
+                  <c:v>3.4373523976001605</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.4396590552528883</c:v>
+                  <c:v>4.0886936518885006</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.0349948424454514</c:v>
+                  <c:v>4.7954691937415186</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.6769749581337861</c:v>
+                  <c:v>5.5571409365139459</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.3651963365424242</c:v>
+                  <c:v>6.3730368146549052</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.099163264852951</c:v>
+                  <c:v>7.2423326378203807</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.87827562516018</c:v>
+                  <c:v>8.1640341019259868</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.7018171608809487</c:v>
+                  <c:v>9.1369594614695764</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.5689440316258949</c:v>
+                  <c:v>10.159723433693284</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.4786739549487784</c:v>
+                  <c:v>11.23072296045088</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>10.429876263821164</c:v>
+                  <c:v>12.348125491504753</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>11.421263232517134</c:v>
+                  <c:v>13.509860466564213</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12.451383037990714</c:v>
+                  <c:v>14.713614656106127</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>13.518614725907701</c:v>
+                  <c:v>15.956831967290009</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>14.621165537565172</c:v>
+                  <c:v>17.236718227318278</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>15.75707092378164</c:v>
+                  <c:v>18.55025132129451</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>16.92419752302742</c:v>
+                  <c:v>19.894196887285382</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>18.120249313222317</c:v>
+                  <c:v>21.26512956403694</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19.342777060715605</c:v>
+                  <c:v>22.659459556686564</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>20.58919108843395</c:v>
+                  <c:v>24.073464046379549</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>21.856777272017318</c:v>
+                  <c:v>25.503322736986838</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>23.142716053347495</c:v>
+                  <c:v>26.945156623246465</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>24.444104141703132</c:v>
+                  <c:v>28.395068896053928</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>25.757978460990234</c:v>
+                  <c:v>29.849186786221171</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>27.081341804295974</c:v>
+                  <c:v>31.303703097546432</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>28.411189580998855</c:v>
+                  <c:v>32.75491619784178</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>29.744536992198743</c:v>
+                  <c:v>34.199267321073556</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>31.078445950879825</c:v>
+                  <c:v>35.633374177671442</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>32.410051075395444</c:v>
+                  <c:v>37.054060061224035</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>33.736584127660429</c:v>
+                  <c:v>38.458377862718919</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>35.055396337729242</c:v>
+                  <c:v>39.843628641166191</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>36.363978149214013</c:v>
+                  <c:v>41.207374635091099</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>37.659976028869885</c:v>
+                  <c:v>42.547446818106778</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>38.94120610151554</c:v>
+                  <c:v>43.861947291773539</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>40.2056644910503</c:v>
+                  <c:v>45.149246962182239</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>41.451534362987609</c:v>
+                  <c:v>46.407979059066705</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>42.677189767975364</c:v>
+                  <c:v>47.637029127307102</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>43.881196474903959</c:v>
+                  <c:v>48.835522153019831</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>45.062310053609281</c:v>
+                  <c:v>50.002807484858771</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>46.219471519573801</c:v>
+                  <c:v>51.138442181873074</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>47.351800886498978</c:v>
+                  <c:v>52.242173369055209</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>48.458588988382367</c:v>
+                  <c:v>53.313920117262327</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>49.539287932846065</c:v>
+                  <c:v>54.353755291625141</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>50.593500534526875</c:v>
+                  <c:v>55.361887737099025</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>51.620969054202554</c:v>
+                  <c:v>56.33864509564529</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>52.621563538852129</c:v>
+                  <c:v>57.284457479769017</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>53.595270022706231</c:v>
+                  <c:v>58.199842163890793</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>54.542178811902794</c:v>
+                  <c:v>59.085389399529127</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>55.462473037600056</c:v>
+                  <c:v>59.941749413036455</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>56.356417625873945</c:v>
+                  <c:v>60.769620605630799</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>57.22434879859312</c:v>
+                  <c:v>61.569738944272203</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>58.066664188500717</c:v>
+                  <c:v>62.342868507857197</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>58.883813624389539</c:v>
+                  <c:v>63.089793135415086</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>59.67629061872519</c:v>
+                  <c:v>63.811309110591687</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>60.444624570326937</c:v>
+                  <c:v>64.508218808811051</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>61.189373678584154</c:v>
+                  <c:v>65.181325229275629</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>61.911118552888134</c:v>
+                  <c:v>65.831427332636551</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>62.610456491152206</c:v>
+                  <c:v>66.459316106066396</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>63.287996394104319</c:v>
+                  <c:v>67.065771280022105</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>63.944354277087427</c:v>
+                  <c:v>67.651558624712223</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>64.580149338028974</c:v>
+                  <c:v>68.217427758786044</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>65.196000538700446</c:v>
+                  <c:v>68.764110407727685</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>65.79252365607492</c:v>
+                  <c:v>69.292319054618503</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>66.370328761231434</c:v>
+                  <c:v>69.802745931138361</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>66.930018084617174</c:v>
+                  <c:v>70.296062301772167</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>67.472184228361968</c:v>
+                  <c:v>70.772917999074224</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>67.997408688580904</c:v>
+                  <c:v>71.233941172452347</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>68.506260653064402</c:v>
+                  <c:v>71.679738217226898</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>68.999296042334976</c:v>
+                  <c:v>72.110893854674558</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>69.477056764661157</c:v>
+                  <c:v>72.527971337376627</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>69.940070158197713</c:v>
+                  <c:v>72.931512757462002</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>70.38884859592136</c:v>
+                  <c:v>73.322039438276519</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>70.823889231416942</c:v>
+                  <c:v>73.700052392641567</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>71.245673865818787</c:v>
+                  <c:v>74.0660328332049</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>71.654668918314272</c:v>
+                  <c:v>74.420442722460024</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>72.051325484557623</c:v>
+                  <c:v>74.763725351834381</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>72.436079469130803</c:v>
+                  <c:v>75.09630594085364</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>72.809351779816552</c:v>
+                  <c:v>75.418592248789878</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>73.17154857292806</c:v>
+                  <c:v>75.730975192425035</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>73.523061540276032</c:v>
+                  <c:v>76.033829464623224</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>73.864268229554</c:v>
+                  <c:v>76.327514149324927</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>74.195532390999304</c:v>
+                  <c:v>76.612373329370442</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>74.51720434414365</c:v>
+                  <c:v>76.888736684241877</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>74.829621359321834</c:v>
+                  <c:v>77.156920075398816</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>75.133108049360686</c:v>
+                  <c:v>77.41722611738281</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>75.427976767538055</c:v>
+                  <c:v>77.669944733291402</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>75.714528008488912</c:v>
+                  <c:v>77.915353693583327</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>75.993050809251301</c:v>
+                  <c:v>78.153719137481275</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>76.263823148096989</c:v>
+                  <c:v>78.385296076494427</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>76.52711233918609</c:v>
+                  <c:v>78.610328879797009</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>76.783175421428723</c:v>
+                  <c:v>78.829051741376844</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>77.032259540235316</c:v>
+                  <c:v>79.041689129013946</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>77.274602321095344</c:v>
+                  <c:v>79.248456215269556</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>77.510432234148894</c:v>
+                  <c:v>79.449559290762721</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>77.739968949103996</c:v>
+                  <c:v>79.645196160087423</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>77.963423680024505</c:v>
+                  <c:v>79.835556520788558</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>78.180999519644161</c:v>
+                  <c:v>80.020822325854581</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>78.392891762991297</c:v>
+                  <c:v>80.201168130226606</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>78.599288220204812</c:v>
+                  <c:v>80.376761421844023</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>78.800369518509257</c:v>
+                  <c:v>80.547762937765313</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>78.996309393387875</c:v>
+                  <c:v>80.714326965911042</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>79.187274969051728</c:v>
+                  <c:v>80.876601632980694</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>79.373427028352296</c:v>
+                  <c:v>81.034729179092977</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>79.554920272324509</c:v>
+                  <c:v>81.188846219695179</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>79.731903569578165</c:v>
+                  <c:v>81.339083995277804</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>79.904520195784443</c:v>
+                  <c:v>81.485568609422714</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>80.072908063517986</c:v>
+                  <c:v>81.628421255696111</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>80.237199942735216</c:v>
+                  <c:v>81.767758433887991</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>80.397523672176675</c:v>
+                  <c:v>81.903692156081831</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>80.554002361989163</c:v>
+                  <c:v>82.03633014302315</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>80.70675458786684</c:v>
+                  <c:v>82.16577601123879</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>80.855894577012037</c:v>
+                  <c:v>82.292129451341992</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>81.001532386215843</c:v>
+                  <c:v>82.415486397941365</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>81.143774072354674</c:v>
+                  <c:v>82.535939191553979</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>81.282721855598481</c:v>
+                  <c:v>82.653576732908903</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>81.41847427561558</c:v>
+                  <c:v>82.768484630005972</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>81.551126341058307</c:v>
+                  <c:v>82.880745338283234</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>81.680769672603915</c:v>
+                  <c:v>82.990438294227815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1218,7 +1427,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A60E-48E2-8EE5-114D8069658F}"/>
+              <c16:uniqueId val="{00000000-0159-45D3-BB1A-53221C80FEE7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1237,6 +1446,8 @@
         <c:axId val="1636145679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="12"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1294,11 +1505,14 @@
         <c:crossAx val="1636148559"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1636148559"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="85"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1402,11 +1616,7 @@
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
   </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
 </c:chartSpace>
 </file>
 
@@ -1966,32 +2176,389 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{484A00C1-80A5-451D-8681-140B61D028FC}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C628EF2-3180-F294-D80A-2FD30DB57909}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9251950" y="2438400"/>
+          <a:ext cx="514350" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>210050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="楕円 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3623D8E-B539-BD13-DE94-5B4B1D8D1123}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12395200" y="2101850"/>
+          <a:ext cx="1080000" cy="1080000"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{845D814E-0670-2B0E-051F-022D0CFC2240}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9194800" y="2603500"/>
+          <a:ext cx="4273550" cy="88900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="二等辺三角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DBD3AB-F9C5-B3F0-9E5D-BAB305F8BA75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10280650" y="2705100"/>
+          <a:ext cx="222250" cy="311150"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="楕円 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06284FED-149D-FC4A-11F9-12FFF05DD976}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11176000" y="2584450"/>
+          <a:ext cx="139700" cy="146050"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80DE176E-CE31-17CE-3AF7-33DDB27C0B3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10375900" y="2470150"/>
+          <a:ext cx="889000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9298609" cy="6079435"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="グラフ 3">
+        <xdr:cNvPr id="2" name="グラフ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE676AF0-CBDD-4DD8-A248-E7F976F66AFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8671FDF8-3575-1FC6-9148-C9CC610FE01F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
+          <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2005,8 +2572,63 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:absoluteAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.03266</cdr:x>
+      <cdr:y>0.29791</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.97922</cdr:x>
+      <cdr:y>0.29791</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="3" name="直線コネクタ 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B8791B1-7976-E8A9-ED05-A08D4498CD49}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="303695" y="1811130"/>
+          <a:ext cx="8801652" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2271,8 +2893,2230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E13D828-1270-416A-99F5-083C9E529C83}">
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.58203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2">
+        <v>16.930143308864643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <f>PI()*4/3*((D3/2)^3-(D4/2)^3)*D2</f>
+        <v>5.8240437158469955E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <f>PI()/4*(D3^2)</f>
+        <v>7.8539816339744835E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <f>0.004</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <f>0.3</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13">
+        <f>PI()/4*(D10^2-D11^2)*D12*D9</f>
+        <v>5.7255526111673989E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <f>0.02</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <f>0.006</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2">
+        <f>PI()/4*(D16^2-D17^2)*D18*D15</f>
+        <v>4.5169819173314044E-2</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2">
+        <v>-0.08</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <f>-D12/2+D21+D3/2</f>
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24">
+        <f>D12/2+D21-D22-D18/2</f>
+        <v>5.4999999999999986E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25">
+        <f>(D5*D23+D13*D21+D19*D24)/(D5+D13+D19)</f>
+        <v>1.7242208301331274E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="2">
+        <f>(D5*D23+D13*D21+D19*D24)/D25</f>
+        <v>5.6719415500328441E-2</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="2">
+        <v>9.81</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="2">
+        <f>ABS(D26*D25/D23)</f>
+        <v>5.433155426591227E-3</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="2">
+        <f>(0.5*D29*D7*D6)/(D28*D31)</f>
+        <v>4.9640657756039583E-2</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="2">
+        <v>60</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="2">
+        <f>DEGREES(ATAN(1^2*D32))</f>
+        <v>2.8418674085524871</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="2">
+        <f>DEGREES(ATAN(3^2*D32))</f>
+        <v>24.073464046379549</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39">
+        <f>SQRT(TAN(RADIANS(D34))/D32)</f>
+        <v>5.9069262689695652</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFB8DC1-0901-4004-AEE1-57169980FD59}">
+  <dimension ref="B2:D131"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <f>計算シート!D32</f>
+        <v>4.9640657756039583E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>DEGREES(ATAN($C$2*B3^2))</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>SQRT(TAN(RADIANS(C3))/$C$2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4">
+        <v>0.1</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C67" si="0">DEGREES(ATAN($C$2*B4^2))</f>
+        <v>2.8441999480523394E-2</v>
+      </c>
+      <c r="D4">
+        <f>SQRT(TAN(RADIANS(C4))/$C$2)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5">
+        <v>0.2</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>0.1137678577491741</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D68" si="1">SQRT(TAN(RADIANS(C5))/$C$2)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6">
+        <v>0.3</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>0.25597631326584203</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7">
+        <v>0.4</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>0.45506246026806418</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>0.71101354533522709</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9">
+        <v>0.6</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1.0238030875477691</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10">
+        <v>0.7</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1.3933833324626947</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11">
+        <v>0.8</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>1.8196760605208775</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12">
+        <v>0.9</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>2.3025617864233912</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>0.90000000000000013</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>2.8418674085524871</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>3.4373523976001605</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15">
+        <v>1.2</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>4.0886936518885006</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16">
+        <v>1.3</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>4.7954691937415186</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>1.3000000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>1.4</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>5.5571409365139459</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
+        <v>1.5</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>6.3730368146549052</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
+        <v>1.6</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>7.2423326378203807</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
+        <v>1.7</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>8.1640341019259868</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
+        <v>1.8</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>9.1369594614695764</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22">
+        <v>1.9</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>10.159723433693284</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>11.23072296045088</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24">
+        <v>2.1</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>12.348125491504753</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>13.509860466564213</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>14.713614656106127</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27">
+        <v>2.4</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>15.956831967290009</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28">
+        <v>2.5</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>17.236718227318278</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29">
+        <v>2.6</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>18.55025132129451</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>2.7</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>19.894196887285382</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31">
+        <v>2.8</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>21.26512956403694</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>2.9</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>22.659459556686564</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>24.073464046379549</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>3.0000000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34">
+        <v>3.1</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>25.503322736986838</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>3.1000000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>3.2</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>26.945156623246465</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36">
+        <v>3.3</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>28.395068896053928</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>3.4</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>29.849186786221171</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38">
+        <v>3.5</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>31.303703097546432</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>3.5000000000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>3.6</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>32.75491619784178</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40">
+        <v>3.7</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>34.199267321073556</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="1"/>
+        <v>3.7000000000000011</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41">
+        <v>3.8</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>35.633374177671442</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42">
+        <v>3.9</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>37.054060061224035</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>38.458377862718919</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>39.843628641166191</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="1"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45">
+        <v>4.2</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>41.207374635091099</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46">
+        <v>4.3</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>42.547446818106778</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="1"/>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>43.861947291773539</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="1"/>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48">
+        <v>4.5</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>45.149246962182239</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>46.407979059066705</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="1"/>
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50">
+        <v>4.7</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>47.637029127307102</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="1"/>
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51">
+        <v>4.8</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>48.835522153019831</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="1"/>
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="0"/>
+        <v>50.002807484858771</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="1"/>
+        <v>4.9000000000000012</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="0"/>
+        <v>51.138442181873074</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="0"/>
+        <v>52.242173369055209</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55">
+        <v>5.2</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>53.313920117262327</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="1"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56">
+        <v>5.3</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>54.353755291625141</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="1"/>
+        <v>5.3000000000000007</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57">
+        <v>5.4</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>55.361887737099025</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="1"/>
+        <v>5.4000000000000012</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58">
+        <v>5.5</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="0"/>
+        <v>56.33864509564529</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59">
+        <v>5.6</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="0"/>
+        <v>57.284457479769017</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="1"/>
+        <v>5.5999999999999988</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60">
+        <v>5.7</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="0"/>
+        <v>58.199842163890793</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="1"/>
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61">
+        <v>5.8</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="0"/>
+        <v>59.085389399529127</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="1"/>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62">
+        <v>5.9</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="0"/>
+        <v>59.941749413036455</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="1"/>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="0"/>
+        <v>60.769620605630799</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000009</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64">
+        <v>6.1</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="0"/>
+        <v>61.569738944272203</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="1"/>
+        <v>6.0999999999999988</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65">
+        <v>6.2</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="0"/>
+        <v>62.342868507857197</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="1"/>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66">
+        <v>6.3</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="0"/>
+        <v>63.089793135415086</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="1"/>
+        <v>6.2999999999999989</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67">
+        <v>6.4</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="0"/>
+        <v>63.811309110591687</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68">
+        <v>6.5</v>
+      </c>
+      <c r="C68">
+        <f t="shared" ref="C68:C131" si="2">DEGREES(ATAN($C$2*B68^2))</f>
+        <v>64.508218808811051</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="1"/>
+        <v>6.5000000000000027</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69">
+        <v>6.6</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="2"/>
+        <v>65.181325229275629</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ref="D69:D131" si="3">SQRT(TAN(RADIANS(C69))/$C$2)</f>
+        <v>6.6000000000000005</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70">
+        <v>6.7</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="2"/>
+        <v>65.831427332636551</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="3"/>
+        <v>6.6999999999999993</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71">
+        <v>6.8</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="2"/>
+        <v>66.459316106066396</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="3"/>
+        <v>6.8000000000000025</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72">
+        <v>6.9</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="2"/>
+        <v>67.065771280022105</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="3"/>
+        <v>6.9000000000000039</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73">
+        <v>7</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="2"/>
+        <v>67.651558624712223</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="3"/>
+        <v>7.0000000000000009</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74">
+        <v>7.1</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="2"/>
+        <v>68.217427758786044</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="3"/>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75">
+        <v>7.2</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="2"/>
+        <v>68.764110407727685</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="3"/>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76">
+        <v>7.3</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="2"/>
+        <v>69.292319054618503</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="3"/>
+        <v>7.3000000000000007</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77">
+        <v>7.4</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="2"/>
+        <v>69.802745931138361</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="3"/>
+        <v>7.4000000000000021</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78">
+        <v>7.5</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="2"/>
+        <v>70.296062301772167</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79">
+        <v>7.6</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="2"/>
+        <v>70.772917999074224</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="3"/>
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80">
+        <v>7.7</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="2"/>
+        <v>71.233941172452347</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="3"/>
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81">
+        <v>7.8</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="2"/>
+        <v>71.679738217226898</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="3"/>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82">
+        <v>7.9</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="2"/>
+        <v>72.110893854674558</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="3"/>
+        <v>7.9000000000000012</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83">
+        <v>8</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="2"/>
+        <v>72.527971337376627</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84">
+        <v>8.1</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="2"/>
+        <v>72.931512757462002</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="3"/>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="2"/>
+        <v>73.322039438276519</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="3"/>
+        <v>8.1999999999999975</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86">
+        <v>8.3000000000000096</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="2"/>
+        <v>73.700052392641567</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="3"/>
+        <v>8.3000000000000131</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87">
+        <v>8.4</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="2"/>
+        <v>74.0660328332049</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="3"/>
+        <v>8.4000000000000021</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88">
+        <v>8.5</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="2"/>
+        <v>74.420442722460024</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89">
+        <v>8.6000000000000103</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="2"/>
+        <v>74.763725351834381</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="3"/>
+        <v>8.6000000000000085</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90">
+        <v>8.7000000000000099</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="2"/>
+        <v>75.09630594085364</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="3"/>
+        <v>8.7000000000000099</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91">
+        <v>8.8000000000000096</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="2"/>
+        <v>75.418592248789878</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="3"/>
+        <v>8.8000000000000078</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92">
+        <v>8.9</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="2"/>
+        <v>75.730975192425035</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="3"/>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93">
+        <v>9.0000000000000107</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="2"/>
+        <v>76.033829464623224</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="3"/>
+        <v>9.0000000000000124</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94">
+        <v>9.1000000000000192</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="2"/>
+        <v>76.327514149324927</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="3"/>
+        <v>9.1000000000000227</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95">
+        <v>9.2000000000000295</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="2"/>
+        <v>76.612373329370442</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="3"/>
+        <v>9.2000000000000295</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96">
+        <v>9.3000000000000398</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="2"/>
+        <v>76.888736684241877</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="3"/>
+        <v>9.300000000000038</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97">
+        <v>9.4000000000000501</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="2"/>
+        <v>77.156920075398816</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="3"/>
+        <v>9.4000000000000483</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98">
+        <v>9.5000000000000604</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="2"/>
+        <v>77.41722611738281</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="3"/>
+        <v>9.5000000000000586</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99">
+        <v>9.6000000000000707</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="2"/>
+        <v>77.669944733291402</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="3"/>
+        <v>9.6000000000000725</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100">
+        <v>9.7000000000000792</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="2"/>
+        <v>77.915353693583327</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="3"/>
+        <v>9.7000000000000792</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101">
+        <v>9.8000000000000895</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="2"/>
+        <v>78.153719137481275</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="3"/>
+        <v>9.8000000000000931</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102">
+        <v>9.9000000000000998</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="2"/>
+        <v>78.385296076494427</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="3"/>
+        <v>9.9000000000000981</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103">
+        <v>10.000000000000099</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="2"/>
+        <v>78.610328879797009</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="3"/>
+        <v>10.000000000000099</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104">
+        <v>10.100000000000099</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="2"/>
+        <v>78.829051741376844</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="3"/>
+        <v>10.100000000000099</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105">
+        <v>10.200000000000101</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="2"/>
+        <v>79.041689129013946</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="3"/>
+        <v>10.200000000000104</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106">
+        <v>10.3000000000001</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="2"/>
+        <v>79.248456215269556</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="3"/>
+        <v>10.300000000000098</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107">
+        <v>10.400000000000199</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="2"/>
+        <v>79.449559290762721</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="3"/>
+        <v>10.400000000000199</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108">
+        <v>10.500000000000201</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="2"/>
+        <v>79.645196160087423</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="3"/>
+        <v>10.500000000000199</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109">
+        <v>10.6000000000002</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="2"/>
+        <v>79.835556520788558</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="3"/>
+        <v>10.600000000000202</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110">
+        <v>10.7000000000002</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="2"/>
+        <v>80.020822325854581</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="3"/>
+        <v>10.700000000000196</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111">
+        <v>10.8000000000002</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="2"/>
+        <v>80.201168130226606</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="3"/>
+        <v>10.800000000000196</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112">
+        <v>10.900000000000199</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="2"/>
+        <v>80.376761421844023</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="3"/>
+        <v>10.900000000000196</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113">
+        <v>11.000000000000201</v>
+      </c>
+      <c r="C113">
+        <f t="shared" si="2"/>
+        <v>80.547762937765313</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="3"/>
+        <v>11.000000000000201</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114">
+        <v>11.1000000000002</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="2"/>
+        <v>80.714326965911042</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="3"/>
+        <v>11.100000000000199</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115">
+        <v>11.2000000000002</v>
+      </c>
+      <c r="C115">
+        <f t="shared" si="2"/>
+        <v>80.876601632980694</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="3"/>
+        <v>11.200000000000198</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116">
+        <v>11.3000000000002</v>
+      </c>
+      <c r="C116">
+        <f t="shared" si="2"/>
+        <v>81.034729179092977</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="3"/>
+        <v>11.30000000000021</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117">
+        <v>11.400000000000301</v>
+      </c>
+      <c r="C117">
+        <f t="shared" si="2"/>
+        <v>81.188846219695179</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="3"/>
+        <v>11.400000000000301</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118">
+        <v>11.5000000000003</v>
+      </c>
+      <c r="C118">
+        <f t="shared" si="2"/>
+        <v>81.339083995277804</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="3"/>
+        <v>11.500000000000302</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119">
+        <v>11.6000000000003</v>
+      </c>
+      <c r="C119">
+        <f t="shared" si="2"/>
+        <v>81.485568609422714</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="3"/>
+        <v>11.6000000000003</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120">
+        <v>11.700000000000299</v>
+      </c>
+      <c r="C120">
+        <f t="shared" si="2"/>
+        <v>81.628421255696111</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="3"/>
+        <v>11.700000000000301</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121">
+        <v>11.800000000000299</v>
+      </c>
+      <c r="C121">
+        <f t="shared" si="2"/>
+        <v>81.767758433887991</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="3"/>
+        <v>11.800000000000301</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122">
+        <v>11.900000000000301</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="2"/>
+        <v>81.903692156081831</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="3"/>
+        <v>11.900000000000302</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123">
+        <v>12.0000000000003</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="2"/>
+        <v>82.03633014302315</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="3"/>
+        <v>12.000000000000306</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124">
+        <v>12.1000000000003</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="2"/>
+        <v>82.16577601123879</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="3"/>
+        <v>12.100000000000298</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125">
+        <v>12.200000000000299</v>
+      </c>
+      <c r="C125">
+        <f t="shared" si="2"/>
+        <v>82.292129451341992</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="3"/>
+        <v>12.200000000000296</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126">
+        <v>12.3000000000004</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="2"/>
+        <v>82.415486397941365</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="3"/>
+        <v>12.300000000000411</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127">
+        <v>12.4000000000004</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="2"/>
+        <v>82.535939191553979</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="3"/>
+        <v>12.400000000000412</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128">
+        <v>12.5000000000004</v>
+      </c>
+      <c r="C128">
+        <f t="shared" si="2"/>
+        <v>82.653576732908903</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="3"/>
+        <v>12.500000000000412</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129">
+        <v>12.600000000000399</v>
+      </c>
+      <c r="C129">
+        <f t="shared" si="2"/>
+        <v>82.768484630005972</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="3"/>
+        <v>12.600000000000408</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130">
+        <v>12.700000000000401</v>
+      </c>
+      <c r="C130">
+        <f t="shared" si="2"/>
+        <v>82.880745338283234</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="3"/>
+        <v>12.700000000000397</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131">
+        <v>12.8000000000004</v>
+      </c>
+      <c r="C131">
+        <f t="shared" si="2"/>
+        <v>82.990438294227815</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="3"/>
+        <v>12.800000000000397</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -2284,7 +5128,7 @@
     <col min="8" max="8" width="8.6640625" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -2301,7 +5145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2327,7 +5171,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2350,7 +5194,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2378,7 +5222,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2403,8 +5247,12 @@
       <c r="G5">
         <v>1.46E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="K5">
+        <f>PI()*4/3*(0.075^3-0.06^3)</f>
+        <v>8.6236718341039815E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2429,8 +5277,12 @@
       <c r="G6">
         <v>8.3500000000000005E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="K6">
+        <f>C5/K5</f>
+        <v>16.930143308864643</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -2458,7 +5310,7 @@
         <v>5.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2486,7 +5338,7 @@
         <v>1.4840579710144935E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2514,7 +5366,7 @@
         <v>0.10350000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2537,7 +5389,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2565,7 +5417,7 @@
         <v>1.7671458676442587E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2590,7 +5442,7 @@
         <v>5.9076923076923108E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -2615,7 +5467,7 @@
         <v>0.33430699841251471</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2643,7 +5495,7 @@
         <v>0.10271983353129474</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2774,1701 +5626,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFB8DC1-0901-4004-AEE1-57169980FD59}">
-  <dimension ref="B2:D131"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2">
-        <v>4.1739999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <f>DEGREES(ATAN($C$2*B3^2))</f>
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f>SQRT(TAN(RADIANS(C3))/$C$2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4">
-        <v>0.1</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:C67" si="0">DEGREES(ATAN($C$2*B4^2))</f>
-        <v>2.3915256979899938E-2</v>
-      </c>
-      <c r="D4">
-        <f>SQRT(TAN(RADIANS(C4))/$C$2)</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5">
-        <v>0.2</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>9.5660944588101454E-2</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ref="D5:D68" si="1">SQRT(TAN(RADIANS(C5))/$C$2)</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6">
-        <v>0.3</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>0.21523631284791431</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7">
-        <v>0.4</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>0.38263844527867291</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8">
-        <v>0.5</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>0.59785975968712479</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9">
-        <v>0.6</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>0.86088451136437993</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10">
-        <v>0.7</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>1.1716843029864481</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11">
-        <v>0.8</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>1.530212609891503</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12">
-        <v>0.9</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>1.9363983361193211</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>2.3901384261256804</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>2.8912895698578218</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15">
-        <v>1.2</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>3.4396590552528883</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16">
-        <v>1.3</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>4.0349948424454514</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="1"/>
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17">
-        <v>1.4</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>4.6769749581337861</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="1"/>
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18">
-        <v>1.5</v>
-      </c>
-      <c r="C18">
-        <f t="shared" si="0"/>
-        <v>5.3651963365424242</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="1"/>
-        <v>1.5000000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19">
-        <v>1.6</v>
-      </c>
-      <c r="C19">
-        <f t="shared" si="0"/>
-        <v>6.099163264852951</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="1"/>
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20">
-        <v>1.7</v>
-      </c>
-      <c r="C20">
-        <f t="shared" si="0"/>
-        <v>6.87827562516018</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="1"/>
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21">
-        <v>1.8</v>
-      </c>
-      <c r="C21">
-        <f t="shared" si="0"/>
-        <v>7.7018171608809487</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="1"/>
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22">
-        <v>1.9</v>
-      </c>
-      <c r="C22">
-        <f t="shared" si="0"/>
-        <v>8.5689440316258949</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="1"/>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="0"/>
-        <v>9.4786739549487784</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24">
-        <v>2.1</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="0"/>
-        <v>10.429876263821164</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="1"/>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="0"/>
-        <v>11.421263232517134</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="0"/>
-        <v>12.451383037990714</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="1"/>
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27">
-        <v>2.4</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="0"/>
-        <v>13.518614725907701</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="1"/>
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28">
-        <v>2.5</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="0"/>
-        <v>14.621165537565172</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29">
-        <v>2.6</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="0"/>
-        <v>15.75707092378164</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="1"/>
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30">
-        <v>2.7</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="0"/>
-        <v>16.92419752302742</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="1"/>
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31">
-        <v>2.8</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="0"/>
-        <v>18.120249313222317</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="1"/>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32">
-        <v>2.9</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="0"/>
-        <v>19.342777060715605</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="1"/>
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33">
-        <v>3</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="0"/>
-        <v>20.58919108843395</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34">
-        <v>3.1</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="0"/>
-        <v>21.856777272017318</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="1"/>
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35">
-        <v>3.2</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="0"/>
-        <v>23.142716053347495</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="1"/>
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36">
-        <v>3.3</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="0"/>
-        <v>24.444104141703132</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37">
-        <v>3.4</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="0"/>
-        <v>25.757978460990234</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="1"/>
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38">
-        <v>3.5</v>
-      </c>
-      <c r="C38">
-        <f t="shared" si="0"/>
-        <v>27.081341804295974</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39">
-        <v>3.6</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="0"/>
-        <v>28.411189580998855</v>
-      </c>
-      <c r="D39">
-        <f t="shared" si="1"/>
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40">
-        <v>3.7</v>
-      </c>
-      <c r="C40">
-        <f t="shared" si="0"/>
-        <v>29.744536992198743</v>
-      </c>
-      <c r="D40">
-        <f t="shared" si="1"/>
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41">
-        <v>3.8</v>
-      </c>
-      <c r="C41">
-        <f t="shared" si="0"/>
-        <v>31.078445950879825</v>
-      </c>
-      <c r="D41">
-        <f t="shared" si="1"/>
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42">
-        <v>3.9</v>
-      </c>
-      <c r="C42">
-        <f t="shared" si="0"/>
-        <v>32.410051075395444</v>
-      </c>
-      <c r="D42">
-        <f t="shared" si="1"/>
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43">
-        <v>4</v>
-      </c>
-      <c r="C43">
-        <f t="shared" si="0"/>
-        <v>33.736584127660429</v>
-      </c>
-      <c r="D43">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C44">
-        <f t="shared" si="0"/>
-        <v>35.055396337729242</v>
-      </c>
-      <c r="D44">
-        <f t="shared" si="1"/>
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45">
-        <v>4.2</v>
-      </c>
-      <c r="C45">
-        <f t="shared" si="0"/>
-        <v>36.363978149214013</v>
-      </c>
-      <c r="D45">
-        <f t="shared" si="1"/>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46">
-        <v>4.3</v>
-      </c>
-      <c r="C46">
-        <f t="shared" si="0"/>
-        <v>37.659976028869885</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="1"/>
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C47">
-        <f t="shared" si="0"/>
-        <v>38.94120610151554</v>
-      </c>
-      <c r="D47">
-        <f t="shared" si="1"/>
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48">
-        <v>4.5</v>
-      </c>
-      <c r="C48">
-        <f t="shared" si="0"/>
-        <v>40.2056644910503</v>
-      </c>
-      <c r="D48">
-        <f t="shared" si="1"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C49">
-        <f t="shared" si="0"/>
-        <v>41.451534362987609</v>
-      </c>
-      <c r="D49">
-        <f t="shared" si="1"/>
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50">
-        <v>4.7</v>
-      </c>
-      <c r="C50">
-        <f t="shared" si="0"/>
-        <v>42.677189767975364</v>
-      </c>
-      <c r="D50">
-        <f t="shared" si="1"/>
-        <v>4.7000000000000011</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51">
-        <v>4.8</v>
-      </c>
-      <c r="C51">
-        <f t="shared" si="0"/>
-        <v>43.881196474903959</v>
-      </c>
-      <c r="D51">
-        <f t="shared" si="1"/>
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C52">
-        <f t="shared" si="0"/>
-        <v>45.062310053609281</v>
-      </c>
-      <c r="D52">
-        <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53">
-        <v>5</v>
-      </c>
-      <c r="C53">
-        <f t="shared" si="0"/>
-        <v>46.219471519573801</v>
-      </c>
-      <c r="D53">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C54">
-        <f t="shared" si="0"/>
-        <v>47.351800886498978</v>
-      </c>
-      <c r="D54">
-        <f t="shared" si="1"/>
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55">
-        <v>5.2</v>
-      </c>
-      <c r="C55">
-        <f t="shared" si="0"/>
-        <v>48.458588988382367</v>
-      </c>
-      <c r="D55">
-        <f t="shared" si="1"/>
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56">
-        <v>5.3</v>
-      </c>
-      <c r="C56">
-        <f t="shared" si="0"/>
-        <v>49.539287932846065</v>
-      </c>
-      <c r="D56">
-        <f t="shared" si="1"/>
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57">
-        <v>5.4</v>
-      </c>
-      <c r="C57">
-        <f t="shared" si="0"/>
-        <v>50.593500534526875</v>
-      </c>
-      <c r="D57">
-        <f t="shared" si="1"/>
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58">
-        <v>5.5</v>
-      </c>
-      <c r="C58">
-        <f t="shared" si="0"/>
-        <v>51.620969054202554</v>
-      </c>
-      <c r="D58">
-        <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59">
-        <v>5.6</v>
-      </c>
-      <c r="C59">
-        <f t="shared" si="0"/>
-        <v>52.621563538852129</v>
-      </c>
-      <c r="D59">
-        <f t="shared" si="1"/>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60">
-        <v>5.7</v>
-      </c>
-      <c r="C60">
-        <f t="shared" si="0"/>
-        <v>53.595270022706231</v>
-      </c>
-      <c r="D60">
-        <f t="shared" si="1"/>
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61">
-        <v>5.8</v>
-      </c>
-      <c r="C61">
-        <f t="shared" si="0"/>
-        <v>54.542178811902794</v>
-      </c>
-      <c r="D61">
-        <f t="shared" si="1"/>
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62">
-        <v>5.9</v>
-      </c>
-      <c r="C62">
-        <f t="shared" si="0"/>
-        <v>55.462473037600056</v>
-      </c>
-      <c r="D62">
-        <f t="shared" si="1"/>
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63">
-        <v>6</v>
-      </c>
-      <c r="C63">
-        <f t="shared" si="0"/>
-        <v>56.356417625873945</v>
-      </c>
-      <c r="D63">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64">
-        <v>6.1</v>
-      </c>
-      <c r="C64">
-        <f t="shared" si="0"/>
-        <v>57.22434879859312</v>
-      </c>
-      <c r="D64">
-        <f t="shared" si="1"/>
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65">
-        <v>6.2</v>
-      </c>
-      <c r="C65">
-        <f t="shared" si="0"/>
-        <v>58.066664188500717</v>
-      </c>
-      <c r="D65">
-        <f t="shared" si="1"/>
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66">
-        <v>6.3</v>
-      </c>
-      <c r="C66">
-        <f t="shared" si="0"/>
-        <v>58.883813624389539</v>
-      </c>
-      <c r="D66">
-        <f t="shared" si="1"/>
-        <v>6.3000000000000007</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67">
-        <v>6.4</v>
-      </c>
-      <c r="C67">
-        <f t="shared" si="0"/>
-        <v>59.67629061872519</v>
-      </c>
-      <c r="D67">
-        <f t="shared" si="1"/>
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68">
-        <v>6.5</v>
-      </c>
-      <c r="C68">
-        <f t="shared" ref="C68:C131" si="2">DEGREES(ATAN($C$2*B68^2))</f>
-        <v>60.444624570326937</v>
-      </c>
-      <c r="D68">
-        <f t="shared" si="1"/>
-        <v>6.4999999999999991</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69">
-        <v>6.6</v>
-      </c>
-      <c r="C69">
-        <f t="shared" si="2"/>
-        <v>61.189373678584154</v>
-      </c>
-      <c r="D69">
-        <f t="shared" ref="D69:D131" si="3">SQRT(TAN(RADIANS(C69))/$C$2)</f>
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70">
-        <v>6.7</v>
-      </c>
-      <c r="C70">
-        <f t="shared" si="2"/>
-        <v>61.911118552888134</v>
-      </c>
-      <c r="D70">
-        <f t="shared" si="3"/>
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71">
-        <v>6.8</v>
-      </c>
-      <c r="C71">
-        <f t="shared" si="2"/>
-        <v>62.610456491152206</v>
-      </c>
-      <c r="D71">
-        <f t="shared" si="3"/>
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72">
-        <v>6.9</v>
-      </c>
-      <c r="C72">
-        <f t="shared" si="2"/>
-        <v>63.287996394104319</v>
-      </c>
-      <c r="D72">
-        <f t="shared" si="3"/>
-        <v>6.9000000000000012</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73">
-        <v>7</v>
-      </c>
-      <c r="C73">
-        <f t="shared" si="2"/>
-        <v>63.944354277087427</v>
-      </c>
-      <c r="D73">
-        <f t="shared" si="3"/>
-        <v>6.9999999999999991</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74">
-        <v>7.1</v>
-      </c>
-      <c r="C74">
-        <f t="shared" si="2"/>
-        <v>64.580149338028974</v>
-      </c>
-      <c r="D74">
-        <f t="shared" si="3"/>
-        <v>7.1000000000000005</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75">
-        <v>7.2</v>
-      </c>
-      <c r="C75">
-        <f t="shared" si="2"/>
-        <v>65.196000538700446</v>
-      </c>
-      <c r="D75">
-        <f t="shared" si="3"/>
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76">
-        <v>7.3</v>
-      </c>
-      <c r="C76">
-        <f t="shared" si="2"/>
-        <v>65.79252365607492</v>
-      </c>
-      <c r="D76">
-        <f t="shared" si="3"/>
-        <v>7.3000000000000007</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="B77">
-        <v>7.4</v>
-      </c>
-      <c r="C77">
-        <f t="shared" si="2"/>
-        <v>66.370328761231434</v>
-      </c>
-      <c r="D77">
-        <f t="shared" si="3"/>
-        <v>7.4000000000000012</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="B78">
-        <v>7.5</v>
-      </c>
-      <c r="C78">
-        <f t="shared" si="2"/>
-        <v>66.930018084617174</v>
-      </c>
-      <c r="D78">
-        <f t="shared" si="3"/>
-        <v>7.5000000000000018</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4">
-      <c r="B79">
-        <v>7.6</v>
-      </c>
-      <c r="C79">
-        <f t="shared" si="2"/>
-        <v>67.472184228361968</v>
-      </c>
-      <c r="D79">
-        <f t="shared" si="3"/>
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80">
-        <v>7.7</v>
-      </c>
-      <c r="C80">
-        <f t="shared" si="2"/>
-        <v>67.997408688580904</v>
-      </c>
-      <c r="D80">
-        <f t="shared" si="3"/>
-        <v>7.6999999999999993</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81">
-        <v>7.8</v>
-      </c>
-      <c r="C81">
-        <f t="shared" si="2"/>
-        <v>68.506260653064402</v>
-      </c>
-      <c r="D81">
-        <f t="shared" si="3"/>
-        <v>7.8000000000000034</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82">
-        <v>7.9</v>
-      </c>
-      <c r="C82">
-        <f t="shared" si="2"/>
-        <v>68.999296042334976</v>
-      </c>
-      <c r="D82">
-        <f t="shared" si="3"/>
-        <v>7.8999999999999995</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="B83">
-        <v>8</v>
-      </c>
-      <c r="C83">
-        <f t="shared" si="2"/>
-        <v>69.477056764661157</v>
-      </c>
-      <c r="D83">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="B84">
-        <v>8.1</v>
-      </c>
-      <c r="C84">
-        <f t="shared" si="2"/>
-        <v>69.940070158197713</v>
-      </c>
-      <c r="D84">
-        <f t="shared" si="3"/>
-        <v>8.1000000000000014</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C85">
-        <f t="shared" si="2"/>
-        <v>70.38884859592136</v>
-      </c>
-      <c r="D85">
-        <f t="shared" si="3"/>
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86">
-        <v>8.3000000000000096</v>
-      </c>
-      <c r="C86">
-        <f t="shared" si="2"/>
-        <v>70.823889231416942</v>
-      </c>
-      <c r="D86">
-        <f t="shared" si="3"/>
-        <v>8.3000000000000131</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87">
-        <v>8.4</v>
-      </c>
-      <c r="C87">
-        <f t="shared" si="2"/>
-        <v>71.245673865818787</v>
-      </c>
-      <c r="D87">
-        <f t="shared" si="3"/>
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88">
-        <v>8.5</v>
-      </c>
-      <c r="C88">
-        <f t="shared" si="2"/>
-        <v>71.654668918314272</v>
-      </c>
-      <c r="D88">
-        <f t="shared" si="3"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89">
-        <v>8.6000000000000103</v>
-      </c>
-      <c r="C89">
-        <f t="shared" si="2"/>
-        <v>72.051325484557623</v>
-      </c>
-      <c r="D89">
-        <f t="shared" si="3"/>
-        <v>8.6000000000000085</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90">
-        <v>8.7000000000000099</v>
-      </c>
-      <c r="C90">
-        <f t="shared" si="2"/>
-        <v>72.436079469130803</v>
-      </c>
-      <c r="D90">
-        <f t="shared" si="3"/>
-        <v>8.7000000000000117</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91">
-        <v>8.8000000000000096</v>
-      </c>
-      <c r="C91">
-        <f t="shared" si="2"/>
-        <v>72.809351779816552</v>
-      </c>
-      <c r="D91">
-        <f t="shared" si="3"/>
-        <v>8.8000000000000096</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92">
-        <v>8.9</v>
-      </c>
-      <c r="C92">
-        <f t="shared" si="2"/>
-        <v>73.17154857292806</v>
-      </c>
-      <c r="D92">
-        <f t="shared" si="3"/>
-        <v>8.8999999999999986</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93">
-        <v>9.0000000000000107</v>
-      </c>
-      <c r="C93">
-        <f t="shared" si="2"/>
-        <v>73.523061540276032</v>
-      </c>
-      <c r="D93">
-        <f t="shared" si="3"/>
-        <v>9.0000000000000142</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94">
-        <v>9.1000000000000192</v>
-      </c>
-      <c r="C94">
-        <f t="shared" si="2"/>
-        <v>73.864268229554</v>
-      </c>
-      <c r="D94">
-        <f t="shared" si="3"/>
-        <v>9.1000000000000174</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95">
-        <v>9.2000000000000295</v>
-      </c>
-      <c r="C95">
-        <f t="shared" si="2"/>
-        <v>74.195532390999304</v>
-      </c>
-      <c r="D95">
-        <f t="shared" si="3"/>
-        <v>9.2000000000000295</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="B96">
-        <v>9.3000000000000398</v>
-      </c>
-      <c r="C96">
-        <f t="shared" si="2"/>
-        <v>74.51720434414365</v>
-      </c>
-      <c r="D96">
-        <f t="shared" si="3"/>
-        <v>9.300000000000038</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97">
-        <v>9.4000000000000501</v>
-      </c>
-      <c r="C97">
-        <f t="shared" si="2"/>
-        <v>74.829621359321834</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="3"/>
-        <v>9.4000000000000483</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98">
-        <v>9.5000000000000604</v>
-      </c>
-      <c r="C98">
-        <f t="shared" si="2"/>
-        <v>75.133108049360686</v>
-      </c>
-      <c r="D98">
-        <f t="shared" si="3"/>
-        <v>9.5000000000000622</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99">
-        <v>9.6000000000000707</v>
-      </c>
-      <c r="C99">
-        <f t="shared" si="2"/>
-        <v>75.427976767538055</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="3"/>
-        <v>9.6000000000000707</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100">
-        <v>9.7000000000000792</v>
-      </c>
-      <c r="C100">
-        <f t="shared" si="2"/>
-        <v>75.714528008488912</v>
-      </c>
-      <c r="D100">
-        <f t="shared" si="3"/>
-        <v>9.7000000000000774</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101">
-        <v>9.8000000000000895</v>
-      </c>
-      <c r="C101">
-        <f t="shared" si="2"/>
-        <v>75.993050809251301</v>
-      </c>
-      <c r="D101">
-        <f t="shared" si="3"/>
-        <v>9.8000000000000895</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102">
-        <v>9.9000000000000998</v>
-      </c>
-      <c r="C102">
-        <f t="shared" si="2"/>
-        <v>76.263823148096989</v>
-      </c>
-      <c r="D102">
-        <f t="shared" si="3"/>
-        <v>9.9000000000000963</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103">
-        <v>10.000000000000099</v>
-      </c>
-      <c r="C103">
-        <f t="shared" si="2"/>
-        <v>76.52711233918609</v>
-      </c>
-      <c r="D103">
-        <f t="shared" si="3"/>
-        <v>10.000000000000107</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104">
-        <v>10.100000000000099</v>
-      </c>
-      <c r="C104">
-        <f t="shared" si="2"/>
-        <v>76.783175421428723</v>
-      </c>
-      <c r="D104">
-        <f t="shared" si="3"/>
-        <v>10.100000000000099</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105">
-        <v>10.200000000000101</v>
-      </c>
-      <c r="C105">
-        <f t="shared" si="2"/>
-        <v>77.032259540235316</v>
-      </c>
-      <c r="D105">
-        <f t="shared" si="3"/>
-        <v>10.200000000000108</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106">
-        <v>10.3000000000001</v>
-      </c>
-      <c r="C106">
-        <f t="shared" si="2"/>
-        <v>77.274602321095344</v>
-      </c>
-      <c r="D106">
-        <f t="shared" si="3"/>
-        <v>10.300000000000098</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107">
-        <v>10.400000000000199</v>
-      </c>
-      <c r="C107">
-        <f t="shared" si="2"/>
-        <v>77.510432234148894</v>
-      </c>
-      <c r="D107">
-        <f t="shared" si="3"/>
-        <v>10.400000000000199</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108">
-        <v>10.500000000000201</v>
-      </c>
-      <c r="C108">
-        <f t="shared" si="2"/>
-        <v>77.739968949103996</v>
-      </c>
-      <c r="D108">
-        <f t="shared" si="3"/>
-        <v>10.500000000000208</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109">
-        <v>10.6000000000002</v>
-      </c>
-      <c r="C109">
-        <f t="shared" si="2"/>
-        <v>77.963423680024505</v>
-      </c>
-      <c r="D109">
-        <f t="shared" si="3"/>
-        <v>10.600000000000202</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110">
-        <v>10.7000000000002</v>
-      </c>
-      <c r="C110">
-        <f t="shared" si="2"/>
-        <v>78.180999519644161</v>
-      </c>
-      <c r="D110">
-        <f t="shared" si="3"/>
-        <v>10.700000000000198</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111">
-        <v>10.8000000000002</v>
-      </c>
-      <c r="C111">
-        <f t="shared" si="2"/>
-        <v>78.392891762991297</v>
-      </c>
-      <c r="D111">
-        <f t="shared" si="3"/>
-        <v>10.800000000000198</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112">
-        <v>10.900000000000199</v>
-      </c>
-      <c r="C112">
-        <f t="shared" si="2"/>
-        <v>78.599288220204812</v>
-      </c>
-      <c r="D112">
-        <f t="shared" si="3"/>
-        <v>10.900000000000205</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
-      <c r="B113">
-        <v>11.000000000000201</v>
-      </c>
-      <c r="C113">
-        <f t="shared" si="2"/>
-        <v>78.800369518509257</v>
-      </c>
-      <c r="D113">
-        <f t="shared" si="3"/>
-        <v>11.000000000000199</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114">
-        <v>11.1000000000002</v>
-      </c>
-      <c r="C114">
-        <f t="shared" si="2"/>
-        <v>78.996309393387875</v>
-      </c>
-      <c r="D114">
-        <f t="shared" si="3"/>
-        <v>11.100000000000202</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115">
-        <v>11.2000000000002</v>
-      </c>
-      <c r="C115">
-        <f t="shared" si="2"/>
-        <v>79.187274969051728</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="3"/>
-        <v>11.200000000000202</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116">
-        <v>11.3000000000002</v>
-      </c>
-      <c r="C116">
-        <f t="shared" si="2"/>
-        <v>79.373427028352296</v>
-      </c>
-      <c r="D116">
-        <f t="shared" si="3"/>
-        <v>11.300000000000201</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
-      <c r="B117">
-        <v>11.400000000000301</v>
-      </c>
-      <c r="C117">
-        <f t="shared" si="2"/>
-        <v>79.554920272324509</v>
-      </c>
-      <c r="D117">
-        <f t="shared" si="3"/>
-        <v>11.400000000000299</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118">
-        <v>11.5000000000003</v>
-      </c>
-      <c r="C118">
-        <f t="shared" si="2"/>
-        <v>79.731903569578165</v>
-      </c>
-      <c r="D118">
-        <f t="shared" si="3"/>
-        <v>11.500000000000302</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119">
-        <v>11.6000000000003</v>
-      </c>
-      <c r="C119">
-        <f t="shared" si="2"/>
-        <v>79.904520195784443</v>
-      </c>
-      <c r="D119">
-        <f t="shared" si="3"/>
-        <v>11.600000000000298</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
-      <c r="B120">
-        <v>11.700000000000299</v>
-      </c>
-      <c r="C120">
-        <f t="shared" si="2"/>
-        <v>80.072908063517986</v>
-      </c>
-      <c r="D120">
-        <f t="shared" si="3"/>
-        <v>11.700000000000298</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121">
-        <v>11.800000000000299</v>
-      </c>
-      <c r="C121">
-        <f t="shared" si="2"/>
-        <v>80.237199942735216</v>
-      </c>
-      <c r="D121">
-        <f t="shared" si="3"/>
-        <v>11.800000000000303</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
-      <c r="B122">
-        <v>11.900000000000301</v>
-      </c>
-      <c r="C122">
-        <f t="shared" si="2"/>
-        <v>80.397523672176675</v>
-      </c>
-      <c r="D122">
-        <f t="shared" si="3"/>
-        <v>11.900000000000299</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
-      <c r="B123">
-        <v>12.0000000000003</v>
-      </c>
-      <c r="C123">
-        <f t="shared" si="2"/>
-        <v>80.554002361989163</v>
-      </c>
-      <c r="D123">
-        <f t="shared" si="3"/>
-        <v>12.000000000000298</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4">
-      <c r="B124">
-        <v>12.1000000000003</v>
-      </c>
-      <c r="C124">
-        <f t="shared" si="2"/>
-        <v>80.70675458786684</v>
-      </c>
-      <c r="D124">
-        <f t="shared" si="3"/>
-        <v>12.100000000000296</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
-      <c r="B125">
-        <v>12.200000000000299</v>
-      </c>
-      <c r="C125">
-        <f t="shared" si="2"/>
-        <v>80.855894577012037</v>
-      </c>
-      <c r="D125">
-        <f t="shared" si="3"/>
-        <v>12.200000000000301</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="B126">
-        <v>12.3000000000004</v>
-      </c>
-      <c r="C126">
-        <f t="shared" si="2"/>
-        <v>81.001532386215843</v>
-      </c>
-      <c r="D126">
-        <f t="shared" si="3"/>
-        <v>12.300000000000402</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="B127">
-        <v>12.4000000000004</v>
-      </c>
-      <c r="C127">
-        <f t="shared" si="2"/>
-        <v>81.143774072354674</v>
-      </c>
-      <c r="D127">
-        <f t="shared" si="3"/>
-        <v>12.400000000000396</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128">
-        <v>12.5000000000004</v>
-      </c>
-      <c r="C128">
-        <f t="shared" si="2"/>
-        <v>81.282721855598481</v>
-      </c>
-      <c r="D128">
-        <f t="shared" si="3"/>
-        <v>12.500000000000396</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129">
-        <v>12.600000000000399</v>
-      </c>
-      <c r="C129">
-        <f t="shared" si="2"/>
-        <v>81.41847427561558</v>
-      </c>
-      <c r="D129">
-        <f t="shared" si="3"/>
-        <v>12.600000000000396</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130">
-        <v>12.700000000000401</v>
-      </c>
-      <c r="C130">
-        <f t="shared" si="2"/>
-        <v>81.551126341058307</v>
-      </c>
-      <c r="D130">
-        <f t="shared" si="3"/>
-        <v>12.700000000000404</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131">
-        <v>12.8000000000004</v>
-      </c>
-      <c r="C131">
-        <f t="shared" si="2"/>
-        <v>81.680769672603915</v>
-      </c>
-      <c r="D131">
-        <f t="shared" si="3"/>
-        <v>12.800000000000402</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>